--- a/templates/marketing-calculators.xlsx
+++ b/templates/marketing-calculators.xlsx
@@ -20,7 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="$#,##0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -94,13 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -469,7 +478,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -516,7 +525,7 @@
           <t>Cost-plus markup (0-1)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -573,7 +582,7 @@
           <t>Cost-plus price</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="6">
         <f>B5*(1+B6)</f>
         <v/>
       </c>
@@ -584,7 +593,7 @@
           <t>Competitor-based price</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="6">
         <f>B7</f>
         <v/>
       </c>
@@ -595,7 +604,7 @@
           <t>Value-based range</t>
         </is>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <f>TEXT(B9,"0.00")&amp;" to "&amp;TEXT(B10,"0.00")</f>
         <v/>
       </c>
@@ -616,13 +625,14 @@
           <t>Contribution per unit at your price</t>
         </is>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="6">
         <f>B16-B5</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -630,7 +640,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -667,7 +677,7 @@
           <t>New product units</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>2000000</v>
       </c>
     </row>
@@ -687,7 +697,7 @@
           <t>Launch marketing</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="9" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -697,7 +707,7 @@
           <t>Extra SG&amp;A</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="9" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -707,7 +717,7 @@
           <t>Share of new sales taken from existing products (0-1)</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -724,7 +734,7 @@
           <t>New product contribution</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="7">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -735,7 +745,7 @@
           <t>Cannibalised contribution</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="7">
         <f>B5*B9*B6</f>
         <v/>
       </c>
@@ -746,13 +756,14 @@
           <t>Incremental contribution</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="7">
         <f>B12-B7-B8-B13</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -760,7 +771,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -797,7 +808,7 @@
           <t>Base sales per week (units)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -807,7 +818,7 @@
           <t>Sales in the promotion week</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -837,7 +848,7 @@
           <t>Store fee or other fixed cost</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="9" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -854,7 +865,7 @@
           <t>Incremental units</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="10">
         <f>B6-B5</f>
         <v/>
       </c>
@@ -865,7 +876,7 @@
           <t>Incremental contribution</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="7">
         <f>B12*B7</f>
         <v/>
       </c>
@@ -876,7 +887,7 @@
           <t>Promotion cost</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="7">
         <f>B8*B6+B9</f>
         <v/>
       </c>
@@ -887,13 +898,14 @@
           <t>Profit from the promotion week</t>
         </is>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <f>B13-B14</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -901,7 +913,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -938,128 +950,128 @@
           <t>Total budget</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="9" t="n">
         <v>200000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Job</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Share of budget (0-1)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>One measure</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>capture</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="13">
         <f>C8*$B$5</f>
         <v/>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>cost per first order</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>awareness</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="12" t="n">
         <v>0.35</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="13">
         <f>C9*$B$5</f>
         <v/>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>reach in target</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>trust</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="12" t="n">
         <v>0.15</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="13">
         <f>C10*$B$5</f>
         <v/>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>referred orders</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>convert</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="13">
         <f>C11*$B$5</f>
         <v/>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>conversion rate</t>
         </is>
@@ -1071,13 +1083,14 @@
           <t>Check</t>
         </is>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="14">
         <f>SUM(C8:C11)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1085,7 +1098,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1117,112 +1130,113 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Leader</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Awareness</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>unaided awareness %</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="13">
         <f>C7-D7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Associations</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>top three words</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr"/>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
+      <c r="C8" s="15" t="inlineStr"/>
+      <c r="D8" s="15" t="inlineStr"/>
+      <c r="E8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Perceived quality</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>price premium held %</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="13">
         <f>C9-D9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Loyalty</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>repeat purchase %</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="8">
+      <c r="D10" s="15" t="inlineStr"/>
+      <c r="E10" s="13">
         <f>C10-D10</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>